--- a/Fase 2/Evidencias proyecto/Documentación/SCRUM/4. Product Backlog.xlsx
+++ b/Fase 2/Evidencias proyecto/Documentación/SCRUM/4. Product Backlog.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t xml:space="preserve">Desarrollo ágil: Pila de Producto (Product Backlog)</t>
   </si>
@@ -97,7 +97,7 @@
     <t xml:space="preserve">Pipeline de limpieza y transformación de datos, preprocesamiento</t>
   </si>
   <si>
-    <t>HU-12</t>
+    <t>HU-05</t>
   </si>
   <si>
     <t xml:space="preserve">Como equipo de desarrollo, necesito estructurar el Documento de Arquitectura de Software (DAS) con diagramas de alto y bajo nivel, con la finalidad de definir la interacción técnica entre la interfaz web, el backend, la API de inferencia y el modelo serializado previo a su construcción.</t>
@@ -106,7 +106,7 @@
     <t xml:space="preserve">Definición de arquitectura y diagramas</t>
   </si>
   <si>
-    <t>HU-05</t>
+    <t>HU-06</t>
   </si>
   <si>
     <t xml:space="preserve">Como equipo de desarrollo, necesito entrenar de forma comparativa diversos algoritmos de aprendizaje automático con el conjunto de datos limpio, con la finalidad de identificar qué modelo presenta la mejor capacidad de ajuste inicial para estimar la carga frutal del Tamarugo.</t>
@@ -121,7 +121,7 @@
     <t xml:space="preserve">Sprint 2</t>
   </si>
   <si>
-    <t>HU-06</t>
+    <t>HU-07</t>
   </si>
   <si>
     <t xml:space="preserve">Como equipo de desarrollo, necesito calcular y comparar las métricas de rendimiento sobre el conjunto de prueba independiente, con la finalidad de fundamentar con rigor matemático la elección del algoritmo final que se integrará en producción.</t>
@@ -130,7 +130,7 @@
     <t xml:space="preserve">Evaluación y selección de modelo</t>
   </si>
   <si>
-    <t>HU-07</t>
+    <t>HU-08</t>
   </si>
   <si>
     <t xml:space="preserve">Como equipo de desarrollo, necesito empaquetar y serializar el modelo seleccionado junto a sus transformaciones de preprocesamiento en un archivo persistente, con la finalidad de facilitar su posterior consumo y carga rápida dentro del backend de la plataforma web.</t>
@@ -139,7 +139,7 @@
     <t xml:space="preserve">Guardado de modelo seleccionado</t>
   </si>
   <si>
-    <t>HU-13</t>
+    <t>HU-09</t>
   </si>
   <si>
     <t xml:space="preserve">Como evaluador docente, necesito revisar el informe de avance intermedio y los artefactos parciales de datos y experimentación, con la finalidad de certificar la continuidad operativa, el ritmo de los Sprints y la viabilidad técnica antes del cierre de la Fase 2.</t>
@@ -148,7 +148,7 @@
     <t xml:space="preserve">Evidencias de avance del proyecto fase 2 CAPSTONE</t>
   </si>
   <si>
-    <t>HU-08</t>
+    <t>HU-10</t>
   </si>
   <si>
     <t xml:space="preserve">Como usuario interesado, necesito una interfaz web clara del sistema, con la finalidad de registrar, explorar de manera intuitiva y visualmente ordenada desde cualquier navegador.</t>
@@ -160,7 +160,7 @@
     <t xml:space="preserve">Sprint 3</t>
   </si>
   <si>
-    <t>HU-09</t>
+    <t>HU-11</t>
   </si>
   <si>
     <t xml:space="preserve">Como equipo de desarrollo, necesito implementar el backend y los endpoints de conexión que reciban los datos del formulario, carguen el modelo serializado y devuelvan la predicción, con la finalidad de habilitar la inferencia matemática automatizada entre la interfaz de usuario y el artefacto de Machine Learning.</t>
@@ -169,16 +169,7 @@
     <t xml:space="preserve">Implementar conexión entre el modelo, API e interfaz web</t>
   </si>
   <si>
-    <t>HU-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como equipo de desarrollo, necesitamos empaquetar y orquestar los servicios de frontend y backend mediante contenedores Docker, con la finalidad de garantizar un despliegue reproducible, aislado y libre de conflictos de dependencias para su evaluación y puesta en marcha.</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>HU-11</t>
+    <t>HU-12</t>
   </si>
   <si>
     <t xml:space="preserve">Como equipo de desarrollo, necesito realizar pruebas de integración extremo a extremo sobre el flujo completo de consulta web, con la finalidad de certificar la robustez del sistema, la coherencia de los resultados calculados y la usabilidad antes de la entrega final.</t>
@@ -187,7 +178,7 @@
     <t xml:space="preserve">Pruebas del sistema</t>
   </si>
   <si>
-    <t>UH-16</t>
+    <t>HU-13</t>
   </si>
   <si>
     <t xml:space="preserve">Como usuario interesado, necesito un botón en la interfaz para descargar o imprimir un comprobante en PDF con los parámetros ingresados y la carga frutal calculada, con la finalidad de disponer de un registro documental portátil que respalde la toma de decisiones ecológicas en terreno.</t>
@@ -202,7 +193,7 @@
     <t xml:space="preserve">Solo si por tiempo da supongo</t>
   </si>
   <si>
-    <t>HU-15</t>
+    <t>HU-14</t>
   </si>
   <si>
     <t xml:space="preserve">Como usuario interesado, necesito registrar una cuenta mediante correo electrónico y contraseña en el formulario web, con la finalidad de disponer de credenciales personales para acceder a las funciones del sistema.</t>
@@ -211,7 +202,7 @@
     <t xml:space="preserve">Registro de usuarios</t>
   </si>
   <si>
-    <t>HU-16</t>
+    <t>HU-15</t>
   </si>
   <si>
     <t xml:space="preserve">Como usuario registrado, necesito iniciar sesión con mis credenciales y poder cerrar mi sesión cuando lo decida, con la finalidad de acceder a la plataforma de forma identificada y resguardar mi sesión activa.</t>
@@ -220,7 +211,7 @@
     <t xml:space="preserve">Inicio y cierre de sesión</t>
   </si>
   <si>
-    <t>HU-17</t>
+    <t>HU-16</t>
   </si>
   <si>
     <t xml:space="preserve">Como sistema, quiero restringir la entrada a módulos de consulta y dashboard mediante el control de roles, con la finalidad de garantizar que solo usuarios autenticados operen la herramienta y que las métricas globales queden reservadas para el administrador.</t>
@@ -229,7 +220,7 @@
     <t xml:space="preserve">Control de acceso y roles</t>
   </si>
   <si>
-    <t>HU-18</t>
+    <t>HU-17</t>
   </si>
   <si>
     <t xml:space="preserve">Como administrador del sistema, quiero visualizar un dashboard interactivo con indicadores consolidados de uso, con la finalidad de conocer el volumen de actividad general, el total de usuarios y las tendencias predictivas registradas en la plataforma.</t>
@@ -238,7 +229,7 @@
     <t xml:space="preserve">Dashboard de administración y métricas globales</t>
   </si>
   <si>
-    <t>HU-19</t>
+    <t>HU-18</t>
   </si>
   <si>
     <t xml:space="preserve">Como usuario autenticado, necesito consultar el historial personal de mis estimaciones de carga frutal, con la finalidad de llevar un registro trazable de las evaluaciones que he realizado en mis visitas a terreno.</t>
@@ -247,7 +238,7 @@
     <t xml:space="preserve">Historial de consultas del usuario regular</t>
   </si>
   <si>
-    <t>HU-14</t>
+    <t>HU-19</t>
   </si>
   <si>
     <t xml:space="preserve">Como evaluador docente, necesito examinar la solución integral terminada, el informe final consolidado y el código fuente documentado, con la finalidad de calificar el cumplimiento de las competencias del perfil de egreso y dar por aprobada la Fase 2 del proyecto de titulación.</t>
@@ -434,6 +425,9 @@
     <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="6" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="0" wrapText="1"/>
     </xf>
@@ -443,9 +437,6 @@
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="1" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="0" vertical="center" wrapText="1"/>
@@ -1183,7 +1174,7 @@
     </row>
     <row r="7" ht="42.75">
       <c r="A7" s="1"/>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="10" t="s">
@@ -1225,7 +1216,7 @@
     </row>
     <row r="8" ht="42.75">
       <c r="A8" s="1"/>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="10" t="s">
@@ -1267,10 +1258,10 @@
     </row>
     <row r="9" ht="42.75">
       <c r="A9" s="1"/>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1309,7 +1300,7 @@
     </row>
     <row r="10" ht="42.75">
       <c r="A10" s="1"/>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C10" s="10" t="s">
@@ -1351,7 +1342,7 @@
     </row>
     <row r="11" ht="42.75">
       <c r="A11" s="1"/>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="10" t="s">
@@ -1393,7 +1384,7 @@
     </row>
     <row r="12" ht="42.75">
       <c r="A12" s="1"/>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C12" s="10" t="s">
@@ -1435,7 +1426,7 @@
     </row>
     <row r="13" ht="42.75">
       <c r="A13" s="1"/>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="10" t="s">
@@ -1477,7 +1468,7 @@
     </row>
     <row r="14" ht="28.5">
       <c r="A14" s="1"/>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="10" t="s">
@@ -1519,10 +1510,10 @@
     </row>
     <row r="15" ht="57">
       <c r="A15" s="1"/>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>48</v>
       </c>
       <c r="D15" s="10" t="s">
@@ -1561,10 +1552,10 @@
     </row>
     <row r="16" ht="42.75">
       <c r="A16" s="1"/>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="15" t="s">
         <v>51</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -1574,15 +1565,15 @@
         <v>32</v>
       </c>
       <c r="F16" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="12"/>
+      <c r="I16" s="17"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -1601,30 +1592,32 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" ht="42.75">
+    <row r="17" hidden="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="18" t="s">
         <v>55</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>32</v>
       </c>
       <c r="F17" s="11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>46</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
-      <c r="I17" s="16"/>
+      <c r="I17" s="18" t="s">
+        <v>57</v>
+      </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1643,32 +1636,30 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" hidden="1">
+    <row r="18" ht="42.75">
       <c r="A18" s="1"/>
-      <c r="B18" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="17" t="s">
+      <c r="B18" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="C18" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="11">
-        <v>2</v>
+      <c r="F18" s="20">
+        <v>3</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>59</v>
+      <c r="H18" s="20" t="s">
+        <v>14</v>
       </c>
-      <c r="I18" s="17" t="s">
-        <v>60</v>
-      </c>
+      <c r="I18" s="21"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1689,7 +1680,7 @@
     </row>
     <row r="19" ht="42.75">
       <c r="A19" s="1"/>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="14" t="s">
         <v>61</v>
       </c>
       <c r="C19" s="19" t="s">
@@ -1702,7 +1693,7 @@
         <v>32</v>
       </c>
       <c r="F19" s="20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>46</v>
@@ -1731,7 +1722,7 @@
     </row>
     <row r="20" ht="42.75">
       <c r="A20" s="1"/>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C20" s="19" t="s">
@@ -1744,7 +1735,7 @@
         <v>32</v>
       </c>
       <c r="F20" s="20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>46</v>
@@ -1773,7 +1764,7 @@
     </row>
     <row r="21" ht="42.75">
       <c r="A21" s="1"/>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="14" t="s">
         <v>67</v>
       </c>
       <c r="C21" s="19" t="s">
@@ -1786,7 +1777,7 @@
         <v>32</v>
       </c>
       <c r="F21" s="20">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>46</v>
@@ -1815,7 +1806,7 @@
     </row>
     <row r="22" ht="42.75">
       <c r="A22" s="1"/>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="14" t="s">
         <v>70</v>
       </c>
       <c r="C22" s="19" t="s">
@@ -1828,7 +1819,7 @@
         <v>32</v>
       </c>
       <c r="F22" s="20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>46</v>
@@ -1857,28 +1848,28 @@
     </row>
     <row r="23" ht="42.75">
       <c r="A23" s="1"/>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="20">
-        <v>5</v>
+      <c r="F23" s="11">
+        <v>2</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="I23" s="21"/>
+      <c r="I23" s="17"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1897,30 +1888,16 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" ht="42.75">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="11">
-        <v>2</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="16"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -29155,34 +29132,6 @@
       <c r="Y996" s="1"/>
       <c r="Z996" s="1"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="1"/>
-      <c r="B997" s="1"/>
-      <c r="C997" s="1"/>
-      <c r="D997" s="3"/>
-      <c r="E997" s="4"/>
-      <c r="F997" s="1"/>
-      <c r="G997" s="1"/>
-      <c r="H997" s="5"/>
-      <c r="I997" s="1"/>
-      <c r="J997" s="1"/>
-      <c r="K997" s="1"/>
-      <c r="L997" s="1"/>
-      <c r="M997" s="1"/>
-      <c r="N997" s="1"/>
-      <c r="O997" s="1"/>
-      <c r="P997" s="1"/>
-      <c r="Q997" s="1"/>
-      <c r="R997" s="1"/>
-      <c r="S997" s="1"/>
-      <c r="T997" s="1"/>
-      <c r="U997" s="1"/>
-      <c r="V997" s="1"/>
-      <c r="W997" s="1"/>
-      <c r="X997" s="1"/>
-      <c r="Y997" s="1"/>
-      <c r="Z997" s="1"/>
-    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
@@ -29191,29 +29140,29 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4" disablePrompts="0">
-        <x14:dataValidation xr:uid="{D1E79FAA-980E-45FD-924A-8447EC6E8BDE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{B051BD7D-632F-438D-8469-56741BB6C935}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Vacía,Planificada,En proceso,Hecho,Descartada"</xm:f>
           </x14:formula1>
-          <xm:sqref>E5:E24</xm:sqref>
+          <xm:sqref>E5:E23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{12058323-9F6A-437D-B5AA-A34C7A2EC885}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{963EC1A4-0D67-4B81-925B-BEBAD10AE184}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Sprint 0,Sprint 1,Sprint 2,Sprint 3"</xm:f>
           </x14:formula1>
-          <xm:sqref>G5:G24</xm:sqref>
+          <xm:sqref>G5:G23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{2839E64D-3369-47B5-A91C-6F40F62C4D2E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{61744BCB-C03A-4898-93EB-BFE6F4E112F2}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>"0,1,2,3,5,8,13,21"</xm:f>
           </x14:formula1>
-          <xm:sqref>F5:F24</xm:sqref>
+          <xm:sqref>F5:F23</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{300B2230-2A13-4685-80EC-ACC1EA45F448}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
+        <x14:dataValidation xr:uid="{7E4AF59B-8F8A-4AD1-958D-36A522C2B49F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Baja,Media,Alta"</xm:f>
           </x14:formula1>
-          <xm:sqref>H5:H24</xm:sqref>
+          <xm:sqref>H5:H23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -29240,7 +29189,7 @@
     <row r="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -29270,7 +29219,7 @@
     <row r="2">
       <c r="A2" s="1"/>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -29328,10 +29277,10 @@
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -29363,7 +29312,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -29395,7 +29344,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -29427,7 +29376,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -29459,7 +29408,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -29491,7 +29440,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -29523,7 +29472,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -29555,7 +29504,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -29587,7 +29536,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
